--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1591,6 +1591,324 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127414992</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kovallberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629355</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7208541</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127414987</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kovallberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629435</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7208601</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127414986</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kovallberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629438</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7208605</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>127414992</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>127414986</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16833-2024 artfynd.xlsx
+++ b/artfynd/A 16833-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119290706</v>
+        <v>119290705</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629281</v>
+        <v>629248</v>
       </c>
       <c r="R2" t="n">
-        <v>7208727</v>
+        <v>7208746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119290705</v>
+        <v>119290706</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629248</v>
+        <v>629281</v>
       </c>
       <c r="R3" t="n">
-        <v>7208746</v>
+        <v>7208727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119290708</v>
+        <v>119290707</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629323</v>
+        <v>629308</v>
       </c>
       <c r="R4" t="n">
-        <v>7208727</v>
+        <v>7208731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119290707</v>
+        <v>119290708</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629308</v>
+        <v>629323</v>
       </c>
       <c r="R5" t="n">
-        <v>7208731</v>
+        <v>7208727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1066,7 @@
         <v>119290709</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119290713</v>
+        <v>119290710</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629303</v>
+        <v>629377</v>
       </c>
       <c r="R7" t="n">
-        <v>7208598</v>
+        <v>7208646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1260,7 @@
         <v>119290711</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119290710</v>
+        <v>119290712</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629377</v>
+        <v>629300</v>
       </c>
       <c r="R9" t="n">
-        <v>7208646</v>
+        <v>7208581</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119290712</v>
+        <v>119290713</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629300</v>
+        <v>629303</v>
       </c>
       <c r="R10" t="n">
-        <v>7208581</v>
+        <v>7208598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127414992</v>
+        <v>127414986</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629355</v>
+        <v>629438</v>
       </c>
       <c r="R11" t="n">
-        <v>7208541</v>
+        <v>7208605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,7 +1657,7 @@
         <v>127414987</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127414986</v>
+        <v>127414992</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629438</v>
+        <v>629355</v>
       </c>
       <c r="R13" t="n">
-        <v>7208605</v>
+        <v>7208541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
